--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,278 +523,278 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>206</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1312</v>
+        <v>1322</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1769</v>
+        <v>1765</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1259</v>
+        <v>1251</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1732</v>
+        <v>1727</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1369</v>
+        <v>1378</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1333</v>
+        <v>1342</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1252</v>
+        <v>1245</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1371</v>
+        <v>1380</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1211</v>
+        <v>1204</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>328</v>
@@ -803,119 +803,119 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>1584</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>164</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1439</v>
+        <v>1444</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -925,25 +925,25 @@
         <v>1265</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -953,44 +953,44 @@
         <v>1329</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>122</v>
@@ -999,7 +999,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -1009,25 +1009,25 @@
         <v>1202</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>1235</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1037,47 +1037,47 @@
         <v>1335</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1411</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>1173</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>938</v>
+        <v>662</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1926</v>
+        <v>2316</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>210</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3">
@@ -558,22 +558,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1045</v>
+        <v>936</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1815</v>
+        <v>1928</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4">
@@ -586,22 +586,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1092</v>
+        <v>1043</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1765</v>
+        <v>1817</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1344</v>
+        <v>1322</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -614,22 +614,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1129</v>
+        <v>1093</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1727</v>
+        <v>1764</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>174</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6">
@@ -642,22 +642,22 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1096</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1758</v>
+        <v>1728</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1228</v>
+        <v>1242</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>209</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1161</v>
+        <v>1099</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1693</v>
+        <v>1755</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1399</v>
+        <v>1364</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>129</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -698,22 +698,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1090</v>
+        <v>1161</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1764</v>
+        <v>1693</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1378</v>
+        <v>1399</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1211</v>
+        <v>1191</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -726,22 +726,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>953</v>
+        <v>1090</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1900</v>
+        <v>1764</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>190</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -754,22 +754,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1010</v>
+        <v>953</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1839</v>
+        <v>1900</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1380</v>
+        <v>1342</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1204</v>
+        <v>1245</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>285</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11">
@@ -782,22 +782,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1199</v>
+        <v>1009</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1646</v>
+        <v>1840</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1415</v>
+        <v>1380</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1167</v>
+        <v>1204</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>328</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -810,22 +810,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1307</v>
+        <v>1200</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1538</v>
+        <v>1645</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1460</v>
+        <v>1415</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1122</v>
+        <v>1167</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>313</v>
+        <v>256</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>117</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
@@ -838,22 +838,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1261</v>
+        <v>1306</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1584</v>
+        <v>1539</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1439</v>
+        <v>1460</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>164</v>
+        <v>314</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>211</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -866,22 +866,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1380</v>
+        <v>1261</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1463</v>
+        <v>1584</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1456</v>
+        <v>1438</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1122</v>
+        <v>1142</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>298</v>
+        <v>163</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>118</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1282</v>
+        <v>1379</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1557</v>
+        <v>1464</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1444</v>
+        <v>1457</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>187</v>
+        <v>299</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -922,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1265</v>
+        <v>1281</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1574</v>
+        <v>1558</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1415</v>
+        <v>1443</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1161</v>
+        <v>1134</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1329</v>
+        <v>1267</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1508</v>
+        <v>1572</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>119</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
@@ -978,22 +978,22 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1307</v>
+        <v>1328</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1529</v>
+        <v>1509</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1180</v>
+        <v>1156</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
@@ -1006,22 +1006,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1202</v>
+        <v>1307</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1633</v>
+        <v>1529</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1340</v>
+        <v>1396</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1235</v>
+        <v>1180</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>211</v>
+        <v>328</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>208</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -1034,22 +1034,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1335</v>
+        <v>1201</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1499</v>
+        <v>1634</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1385</v>
+        <v>1340</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1190</v>
+        <v>1235</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21">
@@ -1062,22 +1062,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1421</v>
+        <v>1337</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1411</v>
+        <v>1497</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1402</v>
+        <v>1385</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2316</v>
+        <v>2351</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1001</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>936</v>
+        <v>662</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1928</v>
+        <v>2315</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>210</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1043</v>
+        <v>933</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1817</v>
+        <v>1931</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1093</v>
+        <v>1046</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1764</v>
+        <v>1814</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1344</v>
+        <v>1322</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1128</v>
+        <v>1093</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1728</v>
+        <v>1764</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>175</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1099</v>
+        <v>1129</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1755</v>
+        <v>1727</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1364</v>
+        <v>1353</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1161</v>
+        <v>1100</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1693</v>
+        <v>1754</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1399</v>
+        <v>1364</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>128</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1090</v>
+        <v>1163</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1764</v>
+        <v>1691</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1378</v>
+        <v>1398</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1211</v>
+        <v>1192</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>953</v>
+        <v>1088</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1900</v>
+        <v>1766</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1342</v>
+        <v>1379</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1245</v>
+        <v>1210</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>207</v>
+        <v>333</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>190</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1009</v>
+        <v>953</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1840</v>
+        <v>1900</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1380</v>
+        <v>1341</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1204</v>
+        <v>1246</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>284</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1200</v>
+        <v>1008</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1645</v>
+        <v>1841</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1415</v>
+        <v>1380</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1167</v>
+        <v>1204</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>256</v>
+        <v>193</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>326</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1306</v>
+        <v>1203</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1539</v>
+        <v>1642</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1460</v>
+        <v>1416</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1122</v>
+        <v>1166</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>116</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1584</v>
+        <v>1540</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1142</v>
+        <v>1123</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>163</v>
+        <v>311</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1379</v>
+        <v>1261</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1464</v>
+        <v>1584</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1457</v>
+        <v>1438</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>299</v>
+        <v>160</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>117</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1281</v>
+        <v>1377</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1558</v>
+        <v>1466</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1443</v>
+        <v>1457</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1134</v>
+        <v>1121</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>185</v>
+        <v>299</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>169</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1267</v>
+        <v>1283</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1572</v>
+        <v>1556</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1416</v>
+        <v>1444</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1160</v>
+        <v>1133</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1328</v>
+        <v>1265</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1509</v>
+        <v>1574</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>118</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1529</v>
+        <v>1511</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1180</v>
+        <v>1156</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1201</v>
+        <v>1306</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1634</v>
+        <v>1530</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1340</v>
+        <v>1397</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>212</v>
+        <v>329</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>209</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1337</v>
+        <v>1206</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1497</v>
+        <v>1629</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1385</v>
+        <v>1341</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1190</v>
+        <v>1234</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>146</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>637</v>
+        <v>761</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2351</v>
+        <v>2234</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1437</v>
+        <v>1386</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>200</v>
+        <v>358</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>268</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2315</v>
+        <v>2350</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>996</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>933</v>
+        <v>660</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1931</v>
+        <v>2317</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>210</v>
+        <v>997</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1046</v>
+        <v>936</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1814</v>
+        <v>1927</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1093</v>
+        <v>1045</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1764</v>
+        <v>1815</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1344</v>
+        <v>1322</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>246</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1129</v>
+        <v>1094</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1727</v>
+        <v>1763</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>172</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1100</v>
+        <v>1131</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1754</v>
+        <v>1725</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1364</v>
+        <v>1353</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1163</v>
+        <v>1100</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1691</v>
+        <v>1754</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1398</v>
+        <v>1363</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1192</v>
+        <v>1229</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>130</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1088</v>
+        <v>1162</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1766</v>
+        <v>1692</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1379</v>
+        <v>1399</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1210</v>
+        <v>1191</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>953</v>
+        <v>1087</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1900</v>
+        <v>1767</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1341</v>
+        <v>1378</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1246</v>
+        <v>1211</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>203</v>
+        <v>332</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>191</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1008</v>
+        <v>952</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1841</v>
+        <v>1901</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1380</v>
+        <v>1341</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1204</v>
+        <v>1246</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>282</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1837</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1381</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>1203</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>1642</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>1416</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>1166</v>
-      </c>
       <c r="G13" s="5" t="n">
-        <v>258</v>
+        <v>195</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>326</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1305</v>
+        <v>1201</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1540</v>
+        <v>1644</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1459</v>
+        <v>1415</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1123</v>
+        <v>1167</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>120</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1261</v>
+        <v>1306</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1584</v>
+        <v>1539</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1142</v>
+        <v>1123</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>213</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1377</v>
+        <v>1260</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1466</v>
+        <v>1585</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1457</v>
+        <v>1438</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>299</v>
+        <v>159</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>115</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1283</v>
+        <v>1379</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1556</v>
+        <v>1464</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1444</v>
+        <v>1458</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>167</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1265</v>
+        <v>1281</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1574</v>
+        <v>1558</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1414</v>
+        <v>1442</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1162</v>
+        <v>1135</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>276</v>
+        <v>187</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1326</v>
+        <v>1263</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1511</v>
+        <v>1576</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>119</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1306</v>
+        <v>1325</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1530</v>
+        <v>1512</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1179</v>
+        <v>1155</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1206</v>
+        <v>1311</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1629</v>
+        <v>1525</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1341</v>
+        <v>1398</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1234</v>
+        <v>1178</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>214</v>
+        <v>330</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,558 +523,558 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>761</v>
+        <v>1019</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2234</v>
+        <v>1979</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1218</v>
+        <v>1283</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1386</v>
+        <v>1323</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>358</v>
+        <v>485</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>637</v>
+        <v>760</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2350</v>
+        <v>2235</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1437</v>
+        <v>1386</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>261</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>660</v>
+        <v>634</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2317</v>
+        <v>2353</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>997</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>936</v>
+        <v>664</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1927</v>
+        <v>2313</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>207</v>
+        <v>996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1045</v>
+        <v>936</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1815</v>
+        <v>1927</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1094</v>
+        <v>1046</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1763</v>
+        <v>1814</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1345</v>
+        <v>1323</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1250</v>
+        <v>1274</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>240</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1131</v>
+        <v>1095</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1725</v>
+        <v>1762</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1100</v>
+        <v>1132</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1754</v>
+        <v>1724</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1363</v>
+        <v>1352</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1162</v>
+        <v>1098</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1692</v>
+        <v>1756</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1399</v>
+        <v>1364</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>131</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1087</v>
+        <v>1162</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1767</v>
+        <v>1692</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1378</v>
+        <v>1398</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1211</v>
+        <v>1192</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>952</v>
+        <v>1086</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1901</v>
+        <v>1768</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1341</v>
+        <v>1378</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1246</v>
+        <v>1211</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>204</v>
+        <v>335</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>188</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1012</v>
+        <v>956</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1837</v>
+        <v>1897</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1381</v>
+        <v>1342</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1203</v>
+        <v>1245</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>282</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1201</v>
+        <v>1010</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1644</v>
+        <v>1839</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1415</v>
+        <v>1379</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>332</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1306</v>
+        <v>1201</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1539</v>
+        <v>1644</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1459</v>
+        <v>1416</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1123</v>
+        <v>1166</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>117</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1260</v>
+        <v>1305</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1585</v>
+        <v>1540</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1142</v>
+        <v>1123</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>159</v>
+        <v>311</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>213</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1379</v>
+        <v>1262</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1464</v>
+        <v>1583</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1458</v>
+        <v>1439</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>305</v>
+        <v>165</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>114</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1281</v>
+        <v>1375</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1558</v>
+        <v>1467</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>167</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1263</v>
+        <v>1280</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1576</v>
+        <v>1559</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1414</v>
+        <v>1442</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1162</v>
+        <v>1135</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1325</v>
+        <v>1263</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1512</v>
+        <v>1576</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>122</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1311</v>
+        <v>1328</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1525</v>
+        <v>1509</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1398</v>
+        <v>1421</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1178</v>
+        <v>1155</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>120</v>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,54 +523,54 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1019</v>
+        <v>998</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1979</v>
+        <v>2002</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>760</v>
+        <v>1013</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2235</v>
+        <v>1984</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1218</v>
+        <v>1283</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1386</v>
+        <v>1323</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>356</v>
+        <v>486</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>127</v>
@@ -579,505 +579,505 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>634</v>
+        <v>752</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2353</v>
+        <v>2237</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1437</v>
+        <v>1386</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>261</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>664</v>
+        <v>631</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2313</v>
+        <v>2348</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>996</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>936</v>
+        <v>631</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1927</v>
+        <v>2234</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>212</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1046</v>
+        <v>939</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1814</v>
+        <v>1923</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1095</v>
+        <v>1045</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1762</v>
+        <v>1814</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1345</v>
+        <v>1323</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1250</v>
+        <v>1274</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1132</v>
+        <v>1096</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1724</v>
+        <v>1761</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>172</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1098</v>
+        <v>1131</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1756</v>
+        <v>1725</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1364</v>
+        <v>1351</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1228</v>
+        <v>1243</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>203</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1162</v>
+        <v>1097</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1692</v>
+        <v>1757</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1398</v>
+        <v>1364</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1192</v>
+        <v>1228</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>133</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1086</v>
+        <v>1161</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1768</v>
+        <v>1693</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1378</v>
+        <v>1399</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1211</v>
+        <v>1191</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>956</v>
+        <v>1085</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1897</v>
+        <v>1769</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>188</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1010</v>
+        <v>955</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1839</v>
+        <v>1898</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1379</v>
+        <v>1340</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>287</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1201</v>
+        <v>1012</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1644</v>
+        <v>1837</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1416</v>
+        <v>1381</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1166</v>
+        <v>1203</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>331</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1305</v>
+        <v>1199</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1540</v>
+        <v>1646</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1459</v>
+        <v>1415</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1123</v>
+        <v>1167</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>115</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1262</v>
+        <v>1306</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1583</v>
+        <v>1539</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1439</v>
+        <v>1459</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1141</v>
+        <v>1123</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>165</v>
+        <v>298</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>212</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1375</v>
+        <v>1262</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1467</v>
+        <v>1583</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1456</v>
+        <v>1439</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>115</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1280</v>
+        <v>1374</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1559</v>
+        <v>1468</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1442</v>
+        <v>1457</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1135</v>
+        <v>1121</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>186</v>
+        <v>295</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>168</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1263</v>
+        <v>1281</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1576</v>
+        <v>1558</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1416</v>
+        <v>1442</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1160</v>
+        <v>1135</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>188</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1328</v>
+        <v>1265</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1509</v>
+        <v>1574</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>998</v>
+        <v>1033</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2002</v>
+        <v>1970</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1984</v>
+        <v>2008</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>486</v>
+        <v>337</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>127</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>752</v>
+        <v>1006</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2237</v>
+        <v>1985</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1218</v>
+        <v>1282</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1386</v>
+        <v>1324</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>344</v>
+        <v>473</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>631</v>
+        <v>747</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2348</v>
+        <v>2234</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1437</v>
+        <v>1386</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>192</v>
+        <v>338</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>284</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>631</v>
+        <v>601</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2234</v>
+        <v>2266</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>963</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>939</v>
+        <v>634</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1923</v>
+        <v>2230</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>221</v>
+        <v>978</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1045</v>
+        <v>939</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1814</v>
+        <v>1922</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1096</v>
+        <v>1044</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1761</v>
+        <v>1815</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1346</v>
+        <v>1323</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1131</v>
+        <v>1097</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1725</v>
+        <v>1760</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>171</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1097</v>
+        <v>1129</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1757</v>
+        <v>1727</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1228</v>
+        <v>1242</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>198</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1161</v>
+        <v>1096</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1693</v>
+        <v>1758</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1191</v>
+        <v>1229</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1085</v>
+        <v>1157</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1769</v>
+        <v>1697</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1378</v>
+        <v>1399</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1211</v>
+        <v>1191</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>101</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>955</v>
+        <v>1089</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1898</v>
+        <v>1765</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1340</v>
+        <v>1378</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1247</v>
+        <v>1211</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>208</v>
+        <v>317</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>197</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1012</v>
+        <v>955</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1837</v>
+        <v>1898</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1381</v>
+        <v>1341</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1203</v>
+        <v>1246</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>281</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1199</v>
+        <v>1010</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1646</v>
+        <v>1839</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1415</v>
+        <v>1379</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>328</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1306</v>
+        <v>1201</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1539</v>
+        <v>1644</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1459</v>
+        <v>1417</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1123</v>
+        <v>1165</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>119</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1262</v>
+        <v>1306</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1583</v>
+        <v>1539</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1439</v>
+        <v>1459</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1141</v>
+        <v>1123</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>200</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1374</v>
+        <v>1258</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1468</v>
+        <v>1586</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1121</v>
+        <v>1143</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1281</v>
+        <v>1373</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1558</v>
+        <v>1469</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1442</v>
+        <v>1457</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1135</v>
+        <v>1121</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>173</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1574</v>
+        <v>1556</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1415</v>
+        <v>1443</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1161</v>
+        <v>1134</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>284</v>
+        <v>199</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1033</v>
+        <v>1228</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1970</v>
+        <v>1776</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>274</v>
+        <v>400</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -558,22 +558,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>991</v>
+        <v>1026</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2008</v>
+        <v>1976</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>337</v>
+        <v>276</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
@@ -586,22 +586,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1985</v>
+        <v>2009</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>473</v>
+        <v>324</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -614,19 +614,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>747</v>
+        <v>1001</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2234</v>
+        <v>1982</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1218</v>
+        <v>1282</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1386</v>
+        <v>1324</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>338</v>
+        <v>467</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>160</v>
@@ -642,22 +642,22 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>601</v>
+        <v>718</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2266</v>
+        <v>2151</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1437</v>
+        <v>1386</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>249</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2230</v>
+        <v>2262</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>978</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8">
@@ -698,22 +698,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>939</v>
+        <v>634</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1922</v>
+        <v>2229</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1320</v>
+        <v>1176</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1279</v>
+        <v>1423</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>209</v>
+        <v>966</v>
       </c>
     </row>
     <row r="9">
@@ -726,22 +726,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1044</v>
+        <v>938</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1815</v>
+        <v>1923</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -754,22 +754,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1097</v>
+        <v>1045</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1760</v>
+        <v>1814</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1345</v>
+        <v>1322</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -782,22 +782,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1129</v>
+        <v>1094</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1727</v>
+        <v>1763</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>164</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -810,22 +810,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1096</v>
+        <v>1129</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1758</v>
+        <v>1727</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -838,22 +838,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1157</v>
+        <v>1091</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1697</v>
+        <v>1763</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1191</v>
+        <v>1229</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14">
@@ -866,22 +866,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1089</v>
+        <v>1161</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1765</v>
+        <v>1693</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1378</v>
+        <v>1399</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1211</v>
+        <v>1191</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>955</v>
+        <v>1089</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1898</v>
+        <v>1765</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1341</v>
+        <v>1379</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1246</v>
+        <v>1210</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>191</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
@@ -922,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1010</v>
+        <v>953</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1839</v>
+        <v>1900</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1379</v>
+        <v>1339</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1205</v>
+        <v>1248</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>280</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1201</v>
+        <v>1012</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1644</v>
+        <v>1837</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1417</v>
+        <v>1381</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1165</v>
+        <v>1203</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>246</v>
+        <v>187</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>331</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18">
@@ -978,22 +978,22 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1306</v>
+        <v>1201</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1539</v>
+        <v>1644</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1459</v>
+        <v>1417</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1123</v>
+        <v>1165</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>103</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19">
@@ -1006,22 +1006,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1258</v>
+        <v>1303</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1586</v>
+        <v>1542</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1437</v>
+        <v>1457</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1143</v>
+        <v>1125</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>208</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
@@ -1034,22 +1034,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1373</v>
+        <v>1257</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1469</v>
+        <v>1587</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1121</v>
+        <v>1143</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>295</v>
+        <v>168</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>126</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
@@ -1062,22 +1062,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1283</v>
+        <v>1375</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1556</v>
+        <v>1467</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1443</v>
+        <v>1458</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1134</v>
+        <v>1120</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,73 +523,73 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1228</v>
+        <v>989</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1776</v>
+        <v>2015</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>400</v>
+        <v>156</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>92</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1026</v>
+        <v>1221</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1976</v>
+        <v>1782</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>276</v>
+        <v>402</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>984</v>
+        <v>1020</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2009</v>
+        <v>1976</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>1272</v>
@@ -598,486 +598,486 @@
         <v>1335</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1001</v>
+        <v>978</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1982</v>
+        <v>2007</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>467</v>
+        <v>317</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>718</v>
+        <v>970</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2151</v>
+        <v>1901</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1218</v>
+        <v>1282</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1386</v>
+        <v>1324</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>350</v>
+        <v>478</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>604</v>
+        <v>723</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2262</v>
+        <v>2145</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1437</v>
+        <v>1386</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>263</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2229</v>
+        <v>2261</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>966</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>938</v>
+        <v>633</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1923</v>
+        <v>2230</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1320</v>
+        <v>1176</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1279</v>
+        <v>1423</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>208</v>
+        <v>964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1045</v>
+        <v>939</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1814</v>
+        <v>1922</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1094</v>
+        <v>1042</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1763</v>
+        <v>1817</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1346</v>
+        <v>1323</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>231</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1129</v>
+        <v>1093</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1727</v>
+        <v>1764</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1091</v>
+        <v>1126</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1763</v>
+        <v>1730</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>203</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1161</v>
+        <v>1094</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1693</v>
+        <v>1760</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1191</v>
+        <v>1229</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1089</v>
+        <v>1162</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1765</v>
+        <v>1692</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1379</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1210</v>
+        <v>1190</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>953</v>
+        <v>1086</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1900</v>
+        <v>1768</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1339</v>
+        <v>1376</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1248</v>
+        <v>1213</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>211</v>
+        <v>322</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>189</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1012</v>
+        <v>956</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1837</v>
+        <v>1897</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1381</v>
+        <v>1342</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1203</v>
+        <v>1245</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>283</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1201</v>
+        <v>1012</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1644</v>
+        <v>1837</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1417</v>
+        <v>1381</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1165</v>
+        <v>1203</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>315</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1303</v>
+        <v>1199</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1542</v>
+        <v>1646</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1457</v>
+        <v>1415</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1125</v>
+        <v>1167</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>111</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1257</v>
+        <v>1302</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1587</v>
+        <v>1543</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1437</v>
+        <v>1457</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1143</v>
+        <v>1125</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>168</v>
+        <v>305</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>214</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1375</v>
+        <v>1258</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1467</v>
+        <v>1586</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1458</v>
+        <v>1438</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1120</v>
+        <v>1142</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>117</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,101 +523,101 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>989</v>
+        <v>1044</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2015</v>
+        <v>1962</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>156</v>
+        <v>267</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>374</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1221</v>
+        <v>981</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1782</v>
+        <v>2022</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>402</v>
+        <v>158</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>91</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1020</v>
+        <v>1214</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1976</v>
+        <v>1783</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>265</v>
+        <v>390</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>153</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>978</v>
+        <v>1013</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2007</v>
+        <v>1975</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>1272</v>
@@ -626,458 +626,458 @@
         <v>1335</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>970</v>
+        <v>948</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1901</v>
+        <v>1925</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>478</v>
+        <v>329</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>723</v>
+        <v>975</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2145</v>
+        <v>1895</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1218</v>
+        <v>1282</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1386</v>
+        <v>1324</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>342</v>
+        <v>470</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>604</v>
+        <v>723</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2261</v>
+        <v>2144</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1164</v>
+        <v>1219</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1436</v>
+        <v>1385</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>201</v>
+        <v>348</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>251</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>633</v>
+        <v>604</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2230</v>
+        <v>2261</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>964</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>939</v>
+        <v>633</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1922</v>
+        <v>2229</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>208</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1042</v>
+        <v>937</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1817</v>
+        <v>1924</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1093</v>
+        <v>1040</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1764</v>
+        <v>1819</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1345</v>
+        <v>1322</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>237</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1126</v>
+        <v>1090</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1730</v>
+        <v>1767</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>167</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1094</v>
+        <v>1130</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1760</v>
+        <v>1726</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1162</v>
+        <v>1093</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1692</v>
+        <v>1761</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1400</v>
+        <v>1364</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1190</v>
+        <v>1228</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>144</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1086</v>
+        <v>1160</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1768</v>
+        <v>1694</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1376</v>
+        <v>1398</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1213</v>
+        <v>1192</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>956</v>
+        <v>1088</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1897</v>
+        <v>1766</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>200</v>
+        <v>312</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>193</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1012</v>
+        <v>956</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1837</v>
+        <v>1897</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1381</v>
+        <v>1342</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1203</v>
+        <v>1245</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>267</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1199</v>
+        <v>1008</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1646</v>
+        <v>1841</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1415</v>
+        <v>1379</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>322</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1302</v>
+        <v>1199</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1543</v>
+        <v>1646</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1457</v>
+        <v>1415</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1125</v>
+        <v>1167</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>117</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1258</v>
+        <v>1305</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1586</v>
+        <v>1540</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1438</v>
+        <v>1458</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1142</v>
+        <v>1124</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>178</v>
+        <v>313</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>205</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,129 +523,129 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1044</v>
+        <v>781</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1962</v>
+        <v>2226</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>267</v>
+        <v>145</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>150</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>981</v>
+        <v>1037</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2022</v>
+        <v>1968</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>371</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1214</v>
+        <v>973</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1783</v>
+        <v>2024</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>390</v>
+        <v>147</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>100</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1013</v>
+        <v>1210</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1975</v>
+        <v>1779</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>257</v>
+        <v>383</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>177</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>948</v>
+        <v>981</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1925</v>
+        <v>1895</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1272</v>
@@ -654,430 +654,430 @@
         <v>1335</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>975</v>
+        <v>951</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1895</v>
+        <v>1921</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>470</v>
+        <v>321</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>723</v>
+        <v>977</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2144</v>
+        <v>1892</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1219</v>
+        <v>1282</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1385</v>
+        <v>1324</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>348</v>
+        <v>475</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>604</v>
+        <v>722</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2261</v>
+        <v>2145</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1164</v>
+        <v>1220</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1436</v>
+        <v>1384</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>249</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>633</v>
+        <v>603</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2229</v>
+        <v>2262</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1424</v>
+        <v>1436</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>965</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>937</v>
+        <v>633</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1924</v>
+        <v>2229</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1320</v>
+        <v>1175</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1279</v>
+        <v>1424</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>201</v>
+        <v>958</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1040</v>
+        <v>935</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1819</v>
+        <v>1926</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1090</v>
+        <v>1038</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1767</v>
+        <v>1821</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1345</v>
+        <v>1322</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>218</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>238</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1130</v>
+        <v>1090</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1726</v>
+        <v>1767</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1351</v>
+        <v>1344</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>178</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1093</v>
+        <v>1131</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1761</v>
+        <v>1725</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1228</v>
+        <v>1242</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>209</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1160</v>
+        <v>1091</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1694</v>
+        <v>1763</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1398</v>
+        <v>1362</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1192</v>
+        <v>1230</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>143</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1088</v>
+        <v>1162</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1766</v>
+        <v>1692</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1378</v>
+        <v>1399</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1211</v>
+        <v>1191</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>956</v>
+        <v>1088</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1897</v>
+        <v>1766</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>175</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1008</v>
+        <v>954</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1841</v>
+        <v>1899</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1379</v>
+        <v>1342</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1205</v>
+        <v>1245</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>278</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1199</v>
+        <v>1008</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1646</v>
+        <v>1841</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1415</v>
+        <v>1379</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>325</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1305</v>
+        <v>1201</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1540</v>
+        <v>1644</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1458</v>
+        <v>1415</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1124</v>
+        <v>1167</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>313</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,157 +523,157 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>781</v>
+        <v>804</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2226</v>
+        <v>2207</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>554</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1037</v>
+        <v>773</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1968</v>
+        <v>2233</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>148</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>973</v>
+        <v>1029</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2024</v>
+        <v>1970</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>382</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1210</v>
+        <v>970</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1779</v>
+        <v>2019</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>383</v>
+        <v>140</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>123</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>981</v>
+        <v>1176</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1895</v>
+        <v>1701</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>270</v>
+        <v>397</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>951</v>
+        <v>986</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1921</v>
+        <v>1889</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1272</v>
@@ -682,63 +682,63 @@
         <v>1335</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>977</v>
+        <v>952</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1892</v>
+        <v>1919</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>475</v>
+        <v>325</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>722</v>
+        <v>976</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2145</v>
+        <v>1893</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1220</v>
+        <v>1283</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1384</v>
+        <v>1323</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>342</v>
+        <v>470</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>130</v>
@@ -747,110 +747,110 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>603</v>
+        <v>720</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2262</v>
+        <v>2147</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1164</v>
+        <v>1220</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1436</v>
+        <v>1384</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>249</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2229</v>
+        <v>2259</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>958</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>935</v>
+        <v>629</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1926</v>
+        <v>2233</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1320</v>
+        <v>1176</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1279</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>213</v>
+        <v>145</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>205</v>
+        <v>962</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1038</v>
+        <v>934</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1821</v>
+        <v>1927</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>207</v>
@@ -859,225 +859,225 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1090</v>
+        <v>1037</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1767</v>
+        <v>1822</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1344</v>
+        <v>1321</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1251</v>
+        <v>1276</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>248</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1131</v>
+        <v>1094</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1725</v>
+        <v>1763</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>171</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1091</v>
+        <v>1129</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1763</v>
+        <v>1727</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1362</v>
+        <v>1351</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>207</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1162</v>
+        <v>1092</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1692</v>
+        <v>1762</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1399</v>
+        <v>1362</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1191</v>
+        <v>1230</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>147</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1088</v>
+        <v>1162</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1766</v>
+        <v>1692</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1378</v>
+        <v>1400</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1211</v>
+        <v>1190</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>954</v>
+        <v>1086</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1899</v>
+        <v>1768</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1342</v>
+        <v>1378</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>213</v>
+        <v>324</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>181</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1008</v>
+        <v>952</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1841</v>
+        <v>1901</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1379</v>
+        <v>1340</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>284</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1201</v>
+        <v>1010</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1644</v>
+        <v>1839</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1415</v>
+        <v>1379</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1167</v>
+        <v>1205</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>313</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,185 +523,185 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2207</v>
+        <v>2190</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1500</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>257</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>773</v>
+        <v>797</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2233</v>
+        <v>2212</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>553</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1029</v>
+        <v>766</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1970</v>
+        <v>2234</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>159</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>970</v>
+        <v>1026</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2019</v>
+        <v>1965</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>140</v>
+        <v>247</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>400</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1176</v>
+        <v>934</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1701</v>
+        <v>1943</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>397</v>
+        <v>155</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>92</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>986</v>
+        <v>1182</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1889</v>
+        <v>1694</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>260</v>
+        <v>386</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>154</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>952</v>
+        <v>987</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1919</v>
+        <v>1887</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1272</v>
@@ -710,175 +710,175 @@
         <v>1335</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>325</v>
+        <v>264</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>976</v>
+        <v>952</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1893</v>
+        <v>1919</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>470</v>
+        <v>321</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>720</v>
+        <v>974</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2147</v>
+        <v>1895</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1220</v>
+        <v>1283</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1384</v>
+        <v>1323</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>342</v>
+        <v>469</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>606</v>
+        <v>721</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2259</v>
+        <v>2146</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1163</v>
+        <v>1219</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1437</v>
+        <v>1385</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>201</v>
+        <v>348</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>243</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2233</v>
+        <v>2263</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>145</v>
+        <v>218</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>962</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>934</v>
+        <v>627</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1927</v>
+        <v>2235</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>207</v>
+        <v>964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1037</v>
+        <v>933</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1822</v>
+        <v>1928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>216</v>
@@ -887,197 +887,197 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1094</v>
+        <v>1042</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1763</v>
+        <v>1817</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1346</v>
+        <v>1323</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>242</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1129</v>
+        <v>1090</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1727</v>
+        <v>1767</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>169</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1092</v>
+        <v>1131</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1762</v>
+        <v>1725</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1362</v>
+        <v>1351</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>212</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1162</v>
+        <v>1092</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1692</v>
+        <v>1762</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1400</v>
+        <v>1363</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1190</v>
+        <v>1229</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>134</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1086</v>
+        <v>1161</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1768</v>
+        <v>1693</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1378</v>
+        <v>1400</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1211</v>
+        <v>1190</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>952</v>
+        <v>1083</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1901</v>
+        <v>1771</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1340</v>
+        <v>1376</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1247</v>
+        <v>1213</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1010</v>
+        <v>955</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1839</v>
+        <v>1898</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1379</v>
+        <v>1340</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>275</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,213 +523,213 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>823</v>
+        <v>657</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2190</v>
+        <v>2357</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1118</v>
+        <v>1040</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1500</v>
+        <v>1579</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>213</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2212</v>
+        <v>2195</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>1500</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>255</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>766</v>
+        <v>789</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2234</v>
+        <v>2214</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>136</v>
+        <v>256</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>561</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1026</v>
+        <v>763</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1965</v>
+        <v>2229</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>247</v>
+        <v>129</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>179</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>934</v>
+        <v>990</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1943</v>
+        <v>1889</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>155</v>
+        <v>260</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>370</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1182</v>
+        <v>941</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1694</v>
+        <v>1935</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>386</v>
+        <v>145</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>99</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>987</v>
+        <v>1183</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1887</v>
+        <v>1692</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1335</v>
+        <v>1280</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>264</v>
+        <v>390</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>149</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>952</v>
+        <v>985</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1919</v>
+        <v>1889</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>1273</v>
@@ -738,346 +738,346 @@
         <v>1334</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>974</v>
+        <v>951</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1895</v>
+        <v>1920</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>469</v>
+        <v>320</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>721</v>
+        <v>975</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2146</v>
+        <v>1894</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1219</v>
+        <v>1282</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1385</v>
+        <v>1324</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>348</v>
+        <v>475</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>602</v>
+        <v>718</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2263</v>
+        <v>2149</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1164</v>
+        <v>1220</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1436</v>
+        <v>1384</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>247</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>627</v>
+        <v>599</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2235</v>
+        <v>2266</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>964</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>933</v>
+        <v>627</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1928</v>
+        <v>2235</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1318</v>
+        <v>1174</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1281</v>
+        <v>1425</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>216</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1042</v>
+        <v>937</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1817</v>
+        <v>1924</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1090</v>
+        <v>1038</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1767</v>
+        <v>1821</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1345</v>
+        <v>1322</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>241</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1131</v>
+        <v>1093</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1725</v>
+        <v>1764</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>174</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1092</v>
+        <v>1129</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1762</v>
+        <v>1727</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1363</v>
+        <v>1352</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>201</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1161</v>
+        <v>1092</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1693</v>
+        <v>1762</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1400</v>
+        <v>1363</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1190</v>
+        <v>1229</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>135</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1083</v>
+        <v>1158</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1771</v>
+        <v>1696</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1376</v>
+        <v>1398</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1213</v>
+        <v>1192</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>955</v>
+        <v>1085</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1898</v>
+        <v>1769</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1340</v>
+        <v>1376</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1247</v>
+        <v>1213</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>180</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -635,7 +635,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -663,7 +663,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -691,7 +691,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -719,7 +719,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -747,7 +747,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -775,7 +775,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -803,7 +803,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -831,7 +831,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -859,7 +859,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -887,7 +887,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -915,7 +915,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -999,7 +999,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -1027,7 +1027,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1055,7 +1055,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>657</v>
+        <v>680</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2357</v>
+        <v>2336</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1040</v>
+        <v>1056</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1579</v>
+        <v>1566</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>487</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -558,22 +558,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>816</v>
+        <v>651</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2195</v>
+        <v>2362</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1118</v>
+        <v>1040</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1500</v>
+        <v>1579</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>211</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4">
@@ -586,22 +586,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>789</v>
+        <v>808</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2214</v>
+        <v>2197</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>264</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
@@ -614,22 +614,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2229</v>
+        <v>2210</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>129</v>
+        <v>250</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>581</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -642,22 +642,22 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>990</v>
+        <v>729</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1889</v>
+        <v>2151</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>148</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>941</v>
+        <v>995</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1935</v>
+        <v>1883</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>378</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -698,22 +698,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1183</v>
+        <v>940</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1692</v>
+        <v>1935</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1280</v>
+        <v>1354</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>390</v>
+        <v>148</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>93</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -726,22 +726,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>985</v>
+        <v>1184</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1889</v>
+        <v>1691</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1273</v>
+        <v>1329</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1334</v>
+        <v>1279</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>260</v>
+        <v>387</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>149</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -754,10 +754,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1920</v>
+        <v>1891</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1273</v>
@@ -766,10 +766,10 @@
         <v>1334</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -782,22 +782,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1894</v>
+        <v>1921</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1282</v>
+        <v>1273</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>475</v>
+        <v>323</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>122</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
@@ -810,22 +810,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>718</v>
+        <v>974</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2149</v>
+        <v>1895</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1220</v>
+        <v>1282</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1384</v>
+        <v>1324</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>365</v>
+        <v>492</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -838,22 +838,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2266</v>
+        <v>2152</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1163</v>
+        <v>1220</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1437</v>
+        <v>1384</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>192</v>
+        <v>341</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>251</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -866,22 +866,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>627</v>
+        <v>600</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2235</v>
+        <v>2265</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1425</v>
+        <v>1438</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>971</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>937</v>
+        <v>628</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1924</v>
+        <v>2234</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1320</v>
+        <v>1175</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1279</v>
+        <v>1424</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>210</v>
+        <v>965</v>
       </c>
     </row>
     <row r="16">
@@ -922,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1038</v>
+        <v>934</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1821</v>
+        <v>1927</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1093</v>
+        <v>1041</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1764</v>
+        <v>1818</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1345</v>
+        <v>1323</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1250</v>
+        <v>1274</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>247</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
@@ -978,22 +978,22 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1129</v>
+        <v>1092</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1727</v>
+        <v>1765</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>162</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19">
@@ -1006,22 +1006,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1092</v>
+        <v>1128</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1762</v>
+        <v>1728</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1363</v>
+        <v>1352</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>202</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20">
@@ -1034,22 +1034,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1158</v>
+        <v>1091</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1696</v>
+        <v>1763</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1398</v>
+        <v>1363</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1192</v>
+        <v>1229</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>142</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21">
@@ -1062,22 +1062,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1085</v>
+        <v>1160</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1769</v>
+        <v>1694</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1376</v>
+        <v>1398</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1213</v>
+        <v>1192</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>94</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,269 +523,269 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>680</v>
+        <v>874</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2336</v>
+        <v>2143</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>272</v>
+        <v>522</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>252</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>651</v>
+        <v>674</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2362</v>
+        <v>2341</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1040</v>
+        <v>1056</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1579</v>
+        <v>1566</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>145</v>
+        <v>273</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>488</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>808</v>
+        <v>642</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2197</v>
+        <v>2365</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1118</v>
+        <v>1040</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1500</v>
+        <v>1579</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>248</v>
+        <v>131</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>219</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2210</v>
+        <v>2193</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>1500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>286</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2151</v>
+        <v>2129</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>550</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>995</v>
+        <v>731</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1883</v>
+        <v>2148</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>253</v>
+        <v>134</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>156</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>940</v>
+        <v>997</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1935</v>
+        <v>1880</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>148</v>
+        <v>256</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>369</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1184</v>
+        <v>939</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1691</v>
+        <v>1936</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1279</v>
+        <v>1354</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>387</v>
+        <v>143</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>95</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>983</v>
+        <v>1182</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1891</v>
+        <v>1693</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>259</v>
+        <v>387</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>950</v>
+        <v>982</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1921</v>
+        <v>1892</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1273</v>
@@ -794,290 +794,290 @@
         <v>1334</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>323</v>
+        <v>261</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>974</v>
+        <v>950</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1895</v>
+        <v>1921</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>492</v>
+        <v>341</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>715</v>
+        <v>970</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2152</v>
+        <v>1899</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1220</v>
+        <v>1283</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1384</v>
+        <v>1323</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>341</v>
+        <v>470</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>600</v>
+        <v>716</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2265</v>
+        <v>2151</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1162</v>
+        <v>1218</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1438</v>
+        <v>1386</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>194</v>
+        <v>341</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>258</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2234</v>
+        <v>2265</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>965</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>934</v>
+        <v>629</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1927</v>
+        <v>2233</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>208</v>
+        <v>961</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1041</v>
+        <v>934</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1818</v>
+        <v>1927</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1092</v>
+        <v>1043</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1765</v>
+        <v>1816</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1345</v>
+        <v>1322</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>233</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1128</v>
+        <v>1090</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1728</v>
+        <v>1767</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>167</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1091</v>
+        <v>1127</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1763</v>
+        <v>1729</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1363</v>
+        <v>1352</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>209</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1160</v>
+        <v>1093</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1694</v>
+        <v>1761</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1398</v>
+        <v>1361</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1192</v>
+        <v>1231</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>130</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,297 +523,297 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>874</v>
+        <v>929</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2143</v>
+        <v>2090</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>522</v>
+        <v>266</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>674</v>
+        <v>869</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2341</v>
+        <v>2147</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>273</v>
+        <v>522</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>252</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>642</v>
+        <v>665</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2365</v>
+        <v>2344</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1040</v>
+        <v>1056</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1579</v>
+        <v>1566</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>131</v>
+        <v>261</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>499</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>804</v>
+        <v>639</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2193</v>
+        <v>2360</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1118</v>
+        <v>1041</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1500</v>
+        <v>1578</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>239</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2129</v>
+        <v>2115</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1500</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2148</v>
+        <v>2124</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>560</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>997</v>
+        <v>733</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1880</v>
+        <v>2145</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>146</v>
+        <v>549</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>939</v>
+        <v>996</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1936</v>
+        <v>1881</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>376</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1182</v>
+        <v>938</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1693</v>
+        <v>1937</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1330</v>
+        <v>1257</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1278</v>
+        <v>1353</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>387</v>
+        <v>142</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>92</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>982</v>
+        <v>1180</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1892</v>
+        <v>1695</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>261</v>
+        <v>390</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>142</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>950</v>
+        <v>983</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1921</v>
+        <v>1891</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>1272</v>
@@ -822,262 +822,262 @@
         <v>1335</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>341</v>
+        <v>278</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>970</v>
+        <v>947</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1899</v>
+        <v>1924</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>470</v>
+        <v>320</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>716</v>
+        <v>969</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2151</v>
+        <v>1900</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1218</v>
+        <v>1281</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1386</v>
+        <v>1325</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>341</v>
+        <v>470</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>600</v>
+        <v>716</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2265</v>
+        <v>2151</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1163</v>
+        <v>1219</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1437</v>
+        <v>1385</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>253</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2233</v>
+        <v>2264</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>961</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>934</v>
+        <v>629</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1927</v>
+        <v>2233</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1320</v>
+        <v>1176</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1279</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>215</v>
+        <v>968</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1043</v>
+        <v>935</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1816</v>
+        <v>1926</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1090</v>
+        <v>1041</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1767</v>
+        <v>1818</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1346</v>
+        <v>1323</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>225</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>240</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1127</v>
+        <v>1090</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>168</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1093</v>
+        <v>1127</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1761</v>
+        <v>1729</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1361</v>
+        <v>1350</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>199</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,325 +523,325 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>929</v>
+        <v>593</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2090</v>
+        <v>2426</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1084</v>
+        <v>993</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1541</v>
+        <v>1634</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>266</v>
+        <v>98</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>152</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>869</v>
+        <v>924</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2147</v>
+        <v>2094</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>522</v>
+        <v>267</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>106</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>665</v>
+        <v>860</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2344</v>
+        <v>2150</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>261</v>
+        <v>509</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>263</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2360</v>
+        <v>2340</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1578</v>
+        <v>1566</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>126</v>
+        <v>256</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>519</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>770</v>
+        <v>607</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2115</v>
+        <v>2279</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1118</v>
+        <v>1041</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1500</v>
+        <v>1578</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>255</v>
+        <v>139</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>205</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2124</v>
+        <v>2111</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>259</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>733</v>
+        <v>759</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2145</v>
+        <v>2122</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>549</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>996</v>
+        <v>733</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1881</v>
+        <v>2145</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1261</v>
+        <v>1145</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1351</v>
+        <v>1467</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>154</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>938</v>
+        <v>994</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1937</v>
+        <v>1883</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>371</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1180</v>
+        <v>937</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1695</v>
+        <v>1938</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1330</v>
+        <v>1257</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1278</v>
+        <v>1353</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>390</v>
+        <v>145</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>87</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>983</v>
+        <v>1180</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1891</v>
+        <v>1695</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1335</v>
+        <v>1279</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>278</v>
+        <v>407</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>146</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1924</v>
+        <v>1895</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1273</v>
@@ -850,234 +850,234 @@
         <v>1334</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>320</v>
+        <v>257</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>969</v>
+        <v>948</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1900</v>
+        <v>1923</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1281</v>
+        <v>1271</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1325</v>
+        <v>1336</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>470</v>
+        <v>320</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>716</v>
+        <v>969</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2151</v>
+        <v>1900</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1219</v>
+        <v>1282</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1385</v>
+        <v>1324</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>347</v>
+        <v>476</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>601</v>
+        <v>717</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2264</v>
+        <v>2150</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1163</v>
+        <v>1219</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1437</v>
+        <v>1385</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>206</v>
+        <v>352</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>251</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2233</v>
+        <v>2264</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>119</v>
+        <v>192</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>968</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>935</v>
+        <v>630</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1926</v>
+        <v>2232</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1319</v>
+        <v>1175</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1280</v>
+        <v>1424</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>201</v>
+        <v>955</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1041</v>
+        <v>933</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1818</v>
+        <v>1928</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1090</v>
+        <v>1041</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1767</v>
+        <v>1818</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1346</v>
+        <v>1323</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>229</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>241</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1127</v>
+        <v>1090</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1729</v>
+        <v>1767</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>159</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,353 +523,353 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>593</v>
+        <v>689</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2426</v>
+        <v>2330</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>993</v>
+        <v>1012</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1634</v>
+        <v>1617</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1001</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>924</v>
+        <v>590</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2094</v>
+        <v>2428</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>267</v>
+        <v>100</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>152</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>860</v>
+        <v>915</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2150</v>
+        <v>2097</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>509</v>
+        <v>254</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>661</v>
+        <v>855</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2340</v>
+        <v>2147</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>256</v>
+        <v>503</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>283</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2279</v>
+        <v>2259</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1578</v>
+        <v>1566</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>484</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>773</v>
+        <v>611</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2111</v>
+        <v>2274</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1118</v>
+        <v>1042</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1500</v>
+        <v>1577</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>248</v>
+        <v>131</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>215</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2122</v>
+        <v>2109</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>249</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>733</v>
+        <v>759</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2145</v>
+        <v>2122</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1467</v>
+        <v>1500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>556</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>994</v>
+        <v>731</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1883</v>
+        <v>2147</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1262</v>
+        <v>1146</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1350</v>
+        <v>1466</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>252</v>
+        <v>129</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>150</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>937</v>
+        <v>992</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1938</v>
+        <v>1885</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>365</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1180</v>
+        <v>938</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1695</v>
+        <v>1937</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1279</v>
+        <v>1354</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>407</v>
+        <v>163</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>91</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>979</v>
+        <v>1174</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1895</v>
+        <v>1701</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>257</v>
+        <v>384</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>146</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>948</v>
+        <v>981</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1923</v>
+        <v>1893</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1271</v>
@@ -878,206 +878,206 @@
         <v>1336</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>969</v>
+        <v>948</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1900</v>
+        <v>1923</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>476</v>
+        <v>327</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>717</v>
+        <v>971</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2150</v>
+        <v>1897</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1219</v>
+        <v>1282</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1385</v>
+        <v>1324</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>352</v>
+        <v>481</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>601</v>
+        <v>717</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2264</v>
+        <v>2150</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1164</v>
+        <v>1220</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1436</v>
+        <v>1384</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>192</v>
+        <v>336</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>257</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>630</v>
+        <v>602</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2232</v>
+        <v>2262</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>955</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>933</v>
+        <v>628</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1928</v>
+        <v>2234</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1320</v>
+        <v>1176</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1279</v>
+        <v>1423</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>207</v>
+        <v>959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1041</v>
+        <v>933</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1818</v>
+        <v>1928</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1090</v>
+        <v>1041</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1767</v>
+        <v>1818</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1344</v>
+        <v>1322</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,381 +523,381 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>689</v>
+        <v>771</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2330</v>
+        <v>2249</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1617</v>
+        <v>1605</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>590</v>
+        <v>684</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2428</v>
+        <v>2334</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>994</v>
+        <v>1012</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1633</v>
+        <v>1617</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>915</v>
+        <v>583</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2097</v>
+        <v>2429</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>254</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>163</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>855</v>
+        <v>910</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2147</v>
+        <v>2094</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>503</v>
+        <v>247</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>137</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>629</v>
+        <v>822</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2259</v>
+        <v>2068</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>270</v>
+        <v>519</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>250</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2274</v>
+        <v>2254</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1577</v>
+        <v>1566</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>492</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>774</v>
+        <v>610</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2109</v>
+        <v>2274</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1117</v>
+        <v>1042</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1501</v>
+        <v>1577</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>205</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2122</v>
+        <v>2108</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>256</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2147</v>
+        <v>2123</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1466</v>
+        <v>1500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>553</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>992</v>
+        <v>731</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1885</v>
+        <v>2147</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1262</v>
+        <v>1146</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1350</v>
+        <v>1466</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>254</v>
+        <v>134</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>143</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>938</v>
+        <v>988</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1937</v>
+        <v>1889</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>369</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1174</v>
+        <v>936</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1701</v>
+        <v>1939</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1330</v>
+        <v>1256</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1278</v>
+        <v>1354</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>384</v>
+        <v>140</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>92</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>981</v>
+        <v>1175</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1893</v>
+        <v>1700</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1271</v>
+        <v>1329</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1336</v>
+        <v>1279</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>258</v>
+        <v>386</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>948</v>
+        <v>982</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1923</v>
+        <v>1892</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>1272</v>
@@ -906,178 +906,178 @@
         <v>1335</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>327</v>
+        <v>263</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1897</v>
+        <v>1925</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1282</v>
+        <v>1271</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>481</v>
+        <v>332</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>717</v>
+        <v>973</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2150</v>
+        <v>1895</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1220</v>
+        <v>1283</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1384</v>
+        <v>1323</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>336</v>
+        <v>467</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>602</v>
+        <v>716</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2262</v>
+        <v>2150</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1163</v>
+        <v>1220</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1437</v>
+        <v>1384</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>202</v>
+        <v>350</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>628</v>
+        <v>601</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2234</v>
+        <v>2263</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1423</v>
+        <v>1437</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>959</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>933</v>
+        <v>628</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1928</v>
+        <v>2234</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1320</v>
+        <v>1176</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1279</v>
+        <v>1423</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>211</v>
+        <v>964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1041</v>
+        <v>936</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1818</v>
+        <v>1925</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +98,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -523,26 +526,26 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>771</v>
+        <v>904</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2249</v>
+        <v>2116</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1605</v>
+        <v>1582</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>175</v>
@@ -551,381 +554,381 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>684</v>
+        <v>764</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2334</v>
+        <v>2255</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1617</v>
+        <v>1605</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>583</v>
+        <v>677</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2429</v>
+        <v>2335</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1633</v>
+        <v>1616</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1009</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>910</v>
+        <v>578</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2094</v>
+        <v>2426</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>186</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>822</v>
+        <v>877</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2068</v>
+        <v>2015</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>519</v>
+        <v>262</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>633</v>
+        <v>829</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2254</v>
+        <v>2059</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>260</v>
+        <v>511</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>261</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2274</v>
+        <v>2255</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1577</v>
+        <v>1566</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>480</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>775</v>
+        <v>611</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2108</v>
+        <v>2273</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1117</v>
+        <v>1042</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1501</v>
+        <v>1577</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>248</v>
+        <v>130</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>208</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2123</v>
+        <v>2110</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2147</v>
+        <v>2125</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1466</v>
+        <v>1500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>547</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>988</v>
+        <v>728</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1889</v>
+        <v>2150</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1262</v>
+        <v>1147</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1350</v>
+        <v>1465</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>147</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>936</v>
+        <v>988</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1939</v>
+        <v>1889</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>372</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1175</v>
+        <v>934</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1700</v>
+        <v>1941</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1279</v>
+        <v>1354</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>386</v>
+        <v>141</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>982</v>
+        <v>1177</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1892</v>
+        <v>1698</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1335</v>
+        <v>1279</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>263</v>
+        <v>389</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>946</v>
+        <v>980</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1925</v>
+        <v>1894</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1271</v>
@@ -934,150 +937,162 @@
         <v>1336</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>332</v>
+        <v>266</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>973</v>
+        <v>952</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1895</v>
+        <v>1919</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>467</v>
+        <v>323</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>716</v>
+        <v>970</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2150</v>
+        <v>1898</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1220</v>
+        <v>1284</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1384</v>
+        <v>1322</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>601</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>2263</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>1163</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>1437</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>252</v>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2234</v>
+        <v>2264</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>964</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>936</v>
+        <v>631</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1925</v>
+        <v>2231</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1320</v>
+        <v>1177</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1279</v>
+        <v>1422</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>202</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,9 +98,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -526,437 +523,437 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>904</v>
+        <v>1032</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2116</v>
+        <v>1988</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>278</v>
+        <v>359</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>175</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>764</v>
+        <v>898</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2255</v>
+        <v>2121</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1605</v>
+        <v>1582</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>677</v>
+        <v>756</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2335</v>
+        <v>2257</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1013</v>
+        <v>1029</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1616</v>
+        <v>1604</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>163</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>578</v>
+        <v>672</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2426</v>
+        <v>2332</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1633</v>
+        <v>1618</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1031</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>877</v>
+        <v>546</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2015</v>
+        <v>2346</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>152</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>829</v>
+        <v>883</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2059</v>
+        <v>2008</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>511</v>
+        <v>254</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>111</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>631</v>
+        <v>826</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2255</v>
+        <v>2061</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1566</v>
+        <v>1530</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>264</v>
+        <v>515</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>250</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2273</v>
+        <v>2253</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1577</v>
+        <v>1565</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>484</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>773</v>
+        <v>610</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2110</v>
+        <v>2274</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1116</v>
+        <v>1042</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1502</v>
+        <v>1577</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>211</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2125</v>
+        <v>2111</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>248</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2150</v>
+        <v>2128</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1147</v>
+        <v>1114</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1465</v>
+        <v>1499</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>148</v>
+        <v>273</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>549</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>988</v>
+        <v>727</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1889</v>
+        <v>2151</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1261</v>
+        <v>1146</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1351</v>
+        <v>1466</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>250</v>
+        <v>127</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>149</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>934</v>
+        <v>989</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1941</v>
+        <v>1888</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>141</v>
+        <v>254</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>380</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1177</v>
+        <v>935</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1698</v>
+        <v>1940</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1329</v>
+        <v>1256</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1279</v>
+        <v>1354</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>389</v>
+        <v>143</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>97</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>980</v>
+        <v>1174</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1894</v>
+        <v>1701</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1271</v>
+        <v>1328</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1336</v>
+        <v>1280</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>266</v>
+        <v>392</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>145</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>952</v>
+        <v>986</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1919</v>
+        <v>1888</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>1273</v>
@@ -965,134 +962,122 @@
         <v>1334</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>970</v>
+        <v>949</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1898</v>
+        <v>1922</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1284</v>
+        <v>1273</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1322</v>
+        <v>1334</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>480</v>
+        <v>336</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1898</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1282</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1324</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>468</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>127</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>600</v>
+        <v>716</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2264</v>
+        <v>2150</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1164</v>
+        <v>1219</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1436</v>
+        <v>1385</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>199</v>
+        <v>344</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>256</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2231</v>
+        <v>2261</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1422</v>
+        <v>1435</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>952</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,465 +523,465 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1032</v>
+        <v>921</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1988</v>
+        <v>2099</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>359</v>
+        <v>164</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>112</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>898</v>
+        <v>1026</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2121</v>
+        <v>1993</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>174</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>756</v>
+        <v>889</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2257</v>
+        <v>2124</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1029</v>
+        <v>1051</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1604</v>
+        <v>1582</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>672</v>
+        <v>751</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2332</v>
+        <v>2254</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1011</v>
+        <v>1028</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1618</v>
+        <v>1605</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>546</v>
+        <v>639</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2346</v>
+        <v>2253</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1633</v>
+        <v>1618</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>95</v>
+        <v>298</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>997</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>883</v>
+        <v>551</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2008</v>
+        <v>2340</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>157</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>826</v>
+        <v>882</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2061</v>
+        <v>2008</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>515</v>
+        <v>259</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>102</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>633</v>
+        <v>828</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2253</v>
+        <v>2059</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1057</v>
+        <v>1095</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1565</v>
+        <v>1530</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>258</v>
+        <v>510</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>253</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2274</v>
+        <v>2254</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1577</v>
+        <v>1565</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>487</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>772</v>
+        <v>608</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2111</v>
+        <v>2276</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1117</v>
+        <v>1043</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1501</v>
+        <v>1576</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>204</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>753</v>
+        <v>770</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2128</v>
+        <v>2113</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>249</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>727</v>
+        <v>753</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2151</v>
+        <v>2128</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1466</v>
+        <v>1500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>552</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>989</v>
+        <v>727</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1888</v>
+        <v>2151</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1261</v>
+        <v>1146</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1351</v>
+        <v>1466</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>254</v>
+        <v>129</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>156</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>935</v>
+        <v>989</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1940</v>
+        <v>1888</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>376</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1174</v>
+        <v>932</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1701</v>
+        <v>1943</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1328</v>
+        <v>1255</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1280</v>
+        <v>1355</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>392</v>
+        <v>147</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>94</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>986</v>
+        <v>1179</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1888</v>
+        <v>1696</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>257</v>
+        <v>382</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>149</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>949</v>
+        <v>984</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1922</v>
+        <v>1890</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>1273</v>
@@ -990,63 +990,63 @@
         <v>1334</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>970</v>
+        <v>948</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1898</v>
+        <v>1923</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1282</v>
+        <v>1271</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>468</v>
+        <v>323</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>716</v>
+        <v>972</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2150</v>
+        <v>1896</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1219</v>
+        <v>1283</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1385</v>
+        <v>1323</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>344</v>
+        <v>472</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>130</v>
@@ -1055,29 +1055,29 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>603</v>
+        <v>717</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2261</v>
+        <v>2149</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1165</v>
+        <v>1220</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1435</v>
+        <v>1384</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>212</v>
+        <v>358</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>244</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,493 +523,493 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>921</v>
+        <v>1052</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2099</v>
+        <v>1968</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1067</v>
+        <v>1087</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1569</v>
+        <v>1549</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>433</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1026</v>
+        <v>914</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1993</v>
+        <v>2105</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>360</v>
+        <v>167</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>111</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>889</v>
+        <v>1018</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2124</v>
+        <v>1995</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>269</v>
+        <v>347</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>185</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>751</v>
+        <v>884</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2254</v>
+        <v>2121</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1605</v>
+        <v>1582</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>318</v>
+        <v>262</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>639</v>
+        <v>718</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2253</v>
+        <v>2175</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1011</v>
+        <v>1028</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1618</v>
+        <v>1605</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>551</v>
+        <v>644</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2340</v>
+        <v>2247</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1633</v>
+        <v>1618</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>86</v>
+        <v>289</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1003</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>882</v>
+        <v>550</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2008</v>
+        <v>2340</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>259</v>
+        <v>92</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>149</v>
+        <v>994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>828</v>
+        <v>883</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2059</v>
+        <v>2006</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>510</v>
+        <v>251</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>632</v>
+        <v>826</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2254</v>
+        <v>2061</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1057</v>
+        <v>1095</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1565</v>
+        <v>1530</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>257</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2276</v>
+        <v>2255</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1576</v>
+        <v>1564</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>133</v>
+        <v>258</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>479</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>770</v>
+        <v>607</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2113</v>
+        <v>2277</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1118</v>
+        <v>1044</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1500</v>
+        <v>1575</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>266</v>
+        <v>151</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>205</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2128</v>
+        <v>2114</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>251</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>727</v>
+        <v>751</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2151</v>
+        <v>2130</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1466</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>560</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>989</v>
+        <v>729</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1888</v>
+        <v>2149</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1261</v>
+        <v>1146</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1351</v>
+        <v>1466</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>256</v>
+        <v>133</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>152</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>932</v>
+        <v>987</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1943</v>
+        <v>1890</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>147</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1179</v>
+        <v>937</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1696</v>
+        <v>1938</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1330</v>
+        <v>1257</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1278</v>
+        <v>1353</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>382</v>
+        <v>136</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>98</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>984</v>
+        <v>1176</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1890</v>
+        <v>1699</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>272</v>
+        <v>394</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>137</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>948</v>
+        <v>984</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1923</v>
+        <v>1890</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1271</v>
@@ -1018,66 +1018,66 @@
         <v>1336</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>323</v>
+        <v>262</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1896</v>
+        <v>1923</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1283</v>
+        <v>1272</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>472</v>
+        <v>326</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>717</v>
+        <v>975</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2149</v>
+        <v>1893</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1220</v>
+        <v>1284</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1384</v>
+        <v>1322</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>358</v>
+        <v>486</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,521 +523,521 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1052</v>
+        <v>816</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1968</v>
+        <v>2204</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1087</v>
+        <v>1002</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1549</v>
+        <v>1634</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>315</v>
+        <v>135</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>146</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>914</v>
+        <v>1046</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2105</v>
+        <v>1973</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1569</v>
+        <v>1548</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>167</v>
+        <v>316</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>431</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1018</v>
+        <v>905</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1995</v>
+        <v>2108</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>347</v>
+        <v>155</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>124</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>884</v>
+        <v>1015</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2121</v>
+        <v>1990</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>262</v>
+        <v>341</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>207</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>718</v>
+        <v>849</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2175</v>
+        <v>2044</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1605</v>
+        <v>1582</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>333</v>
+        <v>276</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>644</v>
+        <v>723</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2247</v>
+        <v>2169</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1011</v>
+        <v>1028</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1618</v>
+        <v>1605</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>550</v>
+        <v>643</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2340</v>
+        <v>2247</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>994</v>
+        <v>1010</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>994</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>883</v>
+        <v>549</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2006</v>
+        <v>2341</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>251</v>
+        <v>86</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>154</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>826</v>
+        <v>882</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2061</v>
+        <v>2007</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1095</v>
+        <v>1085</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>510</v>
+        <v>251</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>631</v>
+        <v>826</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2255</v>
+        <v>2061</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1058</v>
+        <v>1096</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1564</v>
+        <v>1529</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>258</v>
+        <v>514</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>253</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2277</v>
+        <v>2257</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>479</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>769</v>
+        <v>605</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2114</v>
+        <v>2279</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1117</v>
+        <v>1045</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1501</v>
+        <v>1574</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>245</v>
+        <v>130</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>205</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>751</v>
+        <v>769</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2130</v>
+        <v>2114</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>260</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>729</v>
+        <v>752</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2149</v>
+        <v>2129</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1146</v>
+        <v>1114</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1466</v>
+        <v>1499</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>556</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>987</v>
+        <v>727</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1890</v>
+        <v>2151</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1260</v>
+        <v>1145</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1352</v>
+        <v>1467</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>147</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>937</v>
+        <v>988</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1938</v>
+        <v>1889</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>379</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1176</v>
+        <v>936</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1699</v>
+        <v>1939</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1330</v>
+        <v>1256</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1278</v>
+        <v>1354</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>394</v>
+        <v>148</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>86</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>984</v>
+        <v>1176</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1890</v>
+        <v>1699</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1271</v>
+        <v>1330</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1336</v>
+        <v>1278</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>262</v>
+        <v>387</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>948</v>
+        <v>984</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1923</v>
+        <v>1890</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1272</v>
@@ -1046,38 +1046,38 @@
         <v>1335</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1893</v>
+        <v>1921</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1284</v>
+        <v>1272</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>486</v>
+        <v>336</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -635,7 +635,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -663,7 +663,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -691,7 +691,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -719,7 +719,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -747,7 +747,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -775,7 +775,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -803,7 +803,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -831,7 +831,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -859,7 +859,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -887,7 +887,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -915,7 +915,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -999,7 +999,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -1027,7 +1027,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1055,7 +1055,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>816</v>
+        <v>525</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2204</v>
+        <v>2495</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1002</v>
+        <v>874</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1634</v>
+        <v>1764</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>571</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="3">
@@ -558,22 +558,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1046</v>
+        <v>811</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1973</v>
+        <v>2208</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1088</v>
+        <v>1003</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1548</v>
+        <v>1633</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>316</v>
+        <v>137</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>144</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4">
@@ -586,22 +586,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>905</v>
+        <v>1038</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2108</v>
+        <v>1975</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1569</v>
+        <v>1548</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>155</v>
+        <v>305</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>441</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
@@ -614,22 +614,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1015</v>
+        <v>901</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1990</v>
+        <v>2104</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>341</v>
+        <v>149</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>147</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
@@ -642,22 +642,22 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>849</v>
+        <v>980</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2044</v>
+        <v>1913</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>173</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>723</v>
+        <v>853</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2169</v>
+        <v>2039</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1605</v>
+        <v>1582</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
@@ -698,22 +698,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>643</v>
+        <v>725</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2247</v>
+        <v>2166</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1010</v>
+        <v>1028</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1619</v>
+        <v>1605</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
@@ -726,22 +726,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>549</v>
+        <v>641</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2341</v>
+        <v>2249</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1633</v>
+        <v>1618</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>86</v>
+        <v>287</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1000</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -754,22 +754,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>882</v>
+        <v>549</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2007</v>
+        <v>2341</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1085</v>
+        <v>994</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1540</v>
+        <v>1633</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>152</v>
+        <v>999</v>
       </c>
     </row>
     <row r="11">
@@ -782,22 +782,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>826</v>
+        <v>882</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2061</v>
+        <v>2007</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1096</v>
+        <v>1085</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1529</v>
+        <v>1540</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>514</v>
+        <v>257</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
@@ -810,22 +810,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>629</v>
+        <v>822</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2257</v>
+        <v>2065</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1057</v>
+        <v>1097</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1565</v>
+        <v>1528</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>274</v>
+        <v>528</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>259</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -838,22 +838,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>605</v>
+        <v>627</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2279</v>
+        <v>2259</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1045</v>
+        <v>1057</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1574</v>
+        <v>1565</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>479</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
@@ -866,22 +866,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>769</v>
+        <v>606</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2114</v>
+        <v>2278</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1116</v>
+        <v>1043</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1502</v>
+        <v>1576</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>245</v>
+        <v>132</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>213</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>752</v>
+        <v>769</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2129</v>
+        <v>2114</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>254</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
@@ -922,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>727</v>
+        <v>750</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2151</v>
+        <v>2131</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1145</v>
+        <v>1112</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1467</v>
+        <v>1501</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>553</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>988</v>
+        <v>729</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1889</v>
+        <v>2149</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1261</v>
+        <v>1146</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1351</v>
+        <v>1466</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>247</v>
+        <v>127</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>152</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18">
@@ -978,22 +978,22 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>936</v>
+        <v>990</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1939</v>
+        <v>1887</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>365</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
@@ -1006,22 +1006,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1176</v>
+        <v>934</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1699</v>
+        <v>1941</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1330</v>
+        <v>1256</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1278</v>
+        <v>1354</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>387</v>
+        <v>142</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>92</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20">
@@ -1034,22 +1034,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>984</v>
+        <v>1177</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1890</v>
+        <v>1698</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1272</v>
+        <v>1329</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1335</v>
+        <v>1279</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>264</v>
+        <v>387</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>149</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -1062,22 +1062,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>950</v>
+        <v>985</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1921</v>
+        <v>1889</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>336</v>
+        <v>275</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>525</v>
+        <v>442</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2495</v>
+        <v>2551</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>874</v>
+        <v>833</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1764</v>
+        <v>1804</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1052</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>811</v>
+        <v>521</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2208</v>
+        <v>2536</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1003</v>
+        <v>875</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1633</v>
+        <v>1763</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>567</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1038</v>
+        <v>814</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1975</v>
+        <v>2210</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1088</v>
+        <v>1004</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1548</v>
+        <v>1632</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>305</v>
+        <v>126</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>153</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>901</v>
+        <v>1034</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2104</v>
+        <v>1981</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1067</v>
+        <v>1087</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1569</v>
+        <v>1549</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>467</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>980</v>
+        <v>922</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1913</v>
+        <v>2116</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>355</v>
+        <v>156</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>111</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>853</v>
+        <v>984</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2039</v>
+        <v>1908</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>266</v>
+        <v>345</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>725</v>
+        <v>855</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2166</v>
+        <v>2120</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1028</v>
+        <v>1051</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1605</v>
+        <v>1581</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>331</v>
+        <v>271</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>641</v>
+        <v>772</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2249</v>
+        <v>2168</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>549</v>
+        <v>644</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2341</v>
+        <v>2246</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1633</v>
+        <v>1618</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>999</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>882</v>
+        <v>584</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2007</v>
+        <v>2440</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1085</v>
+        <v>994</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1540</v>
+        <v>1632</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>257</v>
+        <v>84</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>150</v>
+        <v>997</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>822</v>
+        <v>920</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2065</v>
+        <v>2011</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1097</v>
+        <v>1086</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>528</v>
+        <v>281</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>102</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>627</v>
+        <v>864</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2259</v>
+        <v>2067</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1057</v>
+        <v>1097</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1565</v>
+        <v>1527</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>254</v>
+        <v>509</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>256</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>606</v>
+        <v>667</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2278</v>
+        <v>2256</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1576</v>
+        <v>1565</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>132</v>
+        <v>257</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>488</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>769</v>
+        <v>604</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2114</v>
+        <v>2377</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1118</v>
+        <v>1044</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1500</v>
+        <v>1575</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>208</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2131</v>
+        <v>2203</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>251</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>729</v>
+        <v>794</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2149</v>
+        <v>2129</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1466</v>
+        <v>1499</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>127</v>
+        <v>261</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>557</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>990</v>
+        <v>774</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1887</v>
+        <v>2146</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1262</v>
+        <v>1147</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1350</v>
+        <v>1465</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>258</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>140</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>934</v>
+        <v>1043</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1941</v>
+        <v>1962</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>374</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1177</v>
+        <v>978</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1698</v>
+        <v>1943</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1329</v>
+        <v>1255</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1279</v>
+        <v>1354</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>387</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>96</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>985</v>
+        <v>1234</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1889</v>
+        <v>1765</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1273</v>
+        <v>1330</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1334</v>
+        <v>1278</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>275</v>
+        <v>394</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>442</v>
+        <v>337</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2551</v>
+        <v>2683</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>833</v>
+        <v>722</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1804</v>
+        <v>1916</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>491</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>521</v>
+        <v>465</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2536</v>
+        <v>2554</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>875</v>
+        <v>834</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1763</v>
+        <v>1804</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1048</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>814</v>
+        <v>513</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2210</v>
+        <v>2500</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1004</v>
+        <v>875</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1632</v>
+        <v>1763</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>577</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1034</v>
+        <v>799</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1981</v>
+        <v>2206</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1087</v>
+        <v>1004</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1549</v>
+        <v>1632</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>312</v>
+        <v>120</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>177</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>922</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2116</v>
+        <v>1893</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1569</v>
+        <v>1550</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>156</v>
+        <v>315</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>450</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>984</v>
+        <v>869</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1908</v>
+        <v>2023</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>345</v>
+        <v>152</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>116</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>855</v>
+        <v>984</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2120</v>
+        <v>1907</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1581</v>
+        <v>1553</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>271</v>
+        <v>349</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>176</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>772</v>
+        <v>854</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2168</v>
+        <v>2037</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1029</v>
+        <v>1052</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1604</v>
+        <v>1581</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>326</v>
+        <v>268</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2246</v>
+        <v>2167</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>584</v>
+        <v>644</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2440</v>
+        <v>2246</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>997</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>920</v>
+        <v>542</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2011</v>
+        <v>2348</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1086</v>
+        <v>995</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1538</v>
+        <v>1632</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>281</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>157</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2067</v>
+        <v>2012</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1097</v>
+        <v>1086</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1527</v>
+        <v>1539</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>509</v>
+        <v>250</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>101</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>667</v>
+        <v>821</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2256</v>
+        <v>2066</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1056</v>
+        <v>1096</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1565</v>
+        <v>1529</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>257</v>
+        <v>510</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>272</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>604</v>
+        <v>630</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2377</v>
+        <v>2256</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>495</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>766</v>
+        <v>603</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2203</v>
+        <v>2281</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1116</v>
+        <v>1042</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1502</v>
+        <v>1577</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>207</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>794</v>
+        <v>767</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2129</v>
+        <v>2116</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>253</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2146</v>
+        <v>2127</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1147</v>
+        <v>1114</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1465</v>
+        <v>1499</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>128</v>
+        <v>264</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>570</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1043</v>
+        <v>731</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1962</v>
+        <v>2147</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1262</v>
+        <v>1147</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1349</v>
+        <v>1465</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>148</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1943</v>
+        <v>1887</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>388</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1234</v>
+        <v>934</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1765</v>
+        <v>1941</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1330</v>
+        <v>1256</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1278</v>
+        <v>1354</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>394</v>
+        <v>152</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>83</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>337</v>
+        <v>420</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2683</v>
+        <v>2601</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1916</v>
+        <v>1885</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>110</v>
+        <v>397</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1117</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>465</v>
+        <v>333</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2554</v>
+        <v>2686</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>834</v>
+        <v>722</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1804</v>
+        <v>1916</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>488</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2500</v>
+        <v>2557</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>875</v>
+        <v>834</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1763</v>
+        <v>1804</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1057</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>799</v>
+        <v>510</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2206</v>
+        <v>2495</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1004</v>
+        <v>875</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1632</v>
+        <v>1763</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>601</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1000</v>
+        <v>766</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1893</v>
+        <v>2127</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1086</v>
+        <v>1004</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1550</v>
+        <v>1632</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>315</v>
+        <v>136</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>143</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>869</v>
+        <v>1003</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2023</v>
+        <v>1889</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1569</v>
+        <v>1550</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>305</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>152</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>984</v>
+        <v>868</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1907</v>
+        <v>2023</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>349</v>
+        <v>157</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>109</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>854</v>
+        <v>983</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2037</v>
+        <v>1908</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1052</v>
+        <v>1083</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1581</v>
+        <v>1552</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>268</v>
+        <v>344</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>172</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2167</v>
+        <v>2038</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1029</v>
+        <v>1052</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1604</v>
+        <v>1581</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>322</v>
+        <v>267</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2246</v>
+        <v>2167</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>147</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>542</v>
+        <v>643</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2348</v>
+        <v>2247</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>995</v>
+        <v>1011</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>103</v>
+        <v>306</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1001</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>877</v>
+        <v>541</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2012</v>
+        <v>2349</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1086</v>
+        <v>995</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1539</v>
+        <v>1632</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>151</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>821</v>
+        <v>876</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2066</v>
+        <v>2013</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1096</v>
+        <v>1085</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1529</v>
+        <v>1540</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>510</v>
+        <v>252</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>109</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>630</v>
+        <v>823</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2256</v>
+        <v>2064</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1057</v>
+        <v>1097</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1565</v>
+        <v>1528</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>264</v>
+        <v>517</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>258</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2281</v>
+        <v>2258</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1577</v>
+        <v>1566</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>480</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>767</v>
+        <v>604</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2116</v>
+        <v>2280</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1117</v>
+        <v>1043</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1501</v>
+        <v>1576</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>210</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2127</v>
+        <v>2116</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>242</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>731</v>
+        <v>753</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2147</v>
+        <v>2128</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1147</v>
+        <v>1114</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1465</v>
+        <v>1499</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>553</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>990</v>
+        <v>730</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1887</v>
+        <v>2148</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1261</v>
+        <v>1147</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1351</v>
+        <v>1465</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>252</v>
+        <v>132</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>155</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>934</v>
+        <v>992</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1941</v>
+        <v>1885</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>364</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>420</v>
+        <v>618</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2601</v>
+        <v>2403</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>754</v>
+        <v>821</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1885</v>
+        <v>1818</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>397</v>
+        <v>699</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>250</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>333</v>
+        <v>414</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2686</v>
+        <v>2606</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1916</v>
+        <v>1885</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>112</v>
+        <v>397</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1115</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>456</v>
+        <v>326</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2557</v>
+        <v>2687</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>834</v>
+        <v>723</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1804</v>
+        <v>1915</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>498</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>510</v>
+        <v>452</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2495</v>
+        <v>2553</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>875</v>
+        <v>834</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1763</v>
+        <v>1804</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1078</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>766</v>
+        <v>476</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2127</v>
+        <v>2417</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1004</v>
+        <v>875</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1632</v>
+        <v>1763</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>569</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
+        <v>769</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2123</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>1003</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>1889</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1086</v>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>1550</v>
+        <v>1633</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>305</v>
+        <v>129</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>152</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>868</v>
+        <v>1002</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2023</v>
+        <v>1889</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1569</v>
+        <v>1550</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>431</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>983</v>
+        <v>869</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1908</v>
+        <v>2022</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1552</v>
+        <v>1569</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>344</v>
+        <v>153</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>113</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>853</v>
+        <v>982</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2038</v>
+        <v>1909</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1052</v>
+        <v>1083</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1581</v>
+        <v>1552</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>267</v>
+        <v>344</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>170</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>724</v>
+        <v>854</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2167</v>
+        <v>2037</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1029</v>
+        <v>1052</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1604</v>
+        <v>1581</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>643</v>
+        <v>722</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2247</v>
+        <v>2169</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>541</v>
+        <v>639</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2349</v>
+        <v>2251</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>995</v>
+        <v>1012</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>81</v>
+        <v>282</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1002</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>876</v>
+        <v>542</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2013</v>
+        <v>2348</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1085</v>
+        <v>995</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1540</v>
+        <v>1632</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>160</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>823</v>
+        <v>877</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2064</v>
+        <v>2012</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1097</v>
+        <v>1084</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1528</v>
+        <v>1541</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>517</v>
+        <v>254</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>628</v>
+        <v>820</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2258</v>
+        <v>2067</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1056</v>
+        <v>1097</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1566</v>
+        <v>1528</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>266</v>
+        <v>521</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>254</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2280</v>
+        <v>2255</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1576</v>
+        <v>1565</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>485</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>767</v>
+        <v>602</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2116</v>
+        <v>2282</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1117</v>
+        <v>1043</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1501</v>
+        <v>1576</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>196</v>
+        <v>469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>753</v>
+        <v>770</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2128</v>
+        <v>2113</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>248</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2148</v>
+        <v>2130</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1147</v>
+        <v>1114</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1465</v>
+        <v>1499</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>558</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>992</v>
+        <v>732</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1885</v>
+        <v>2146</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1261</v>
+        <v>1146</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1351</v>
+        <v>1466</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>145</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>618</v>
+        <v>672</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2403</v>
+        <v>2349</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1818</v>
+        <v>1801</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>699</v>
+        <v>331</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>414</v>
+        <v>612</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2606</v>
+        <v>2408</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>754</v>
+        <v>821</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1885</v>
+        <v>1818</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>397</v>
+        <v>698</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>248</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>326</v>
+        <v>409</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2687</v>
+        <v>2605</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1915</v>
+        <v>1884</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1121</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>452</v>
+        <v>322</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2553</v>
+        <v>2683</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>834</v>
+        <v>723</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1804</v>
+        <v>1915</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>522</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>476</v>
+        <v>418</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2417</v>
+        <v>2475</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>875</v>
+        <v>834</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1763</v>
+        <v>1804</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1046</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>769</v>
+        <v>479</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2123</v>
+        <v>2413</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1003</v>
+        <v>874</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1633</v>
+        <v>1764</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>577</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1002</v>
+        <v>769</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1889</v>
+        <v>2122</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1086</v>
+        <v>1003</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1550</v>
+        <v>1633</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>306</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>144</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>869</v>
+        <v>1002</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2022</v>
+        <v>1889</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1569</v>
+        <v>1550</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>430</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>982</v>
+        <v>867</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1909</v>
+        <v>2024</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1552</v>
+        <v>1569</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>344</v>
+        <v>153</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>112</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>854</v>
+        <v>982</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2037</v>
+        <v>1909</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1052</v>
+        <v>1083</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1581</v>
+        <v>1552</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>269</v>
+        <v>345</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>166</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>722</v>
+        <v>853</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2169</v>
+        <v>2038</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1029</v>
+        <v>1053</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1604</v>
+        <v>1580</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>639</v>
+        <v>718</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2251</v>
+        <v>2173</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1012</v>
+        <v>1029</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1617</v>
+        <v>1604</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>153</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>542</v>
+        <v>640</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2348</v>
+        <v>2250</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1632</v>
+        <v>1616</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>88</v>
+        <v>289</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1005</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>877</v>
+        <v>543</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2012</v>
+        <v>2346</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>254</v>
+        <v>90</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>154</v>
+        <v>999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>820</v>
+        <v>874</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2067</v>
+        <v>2015</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1097</v>
+        <v>1084</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1528</v>
+        <v>1541</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>521</v>
+        <v>259</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>101</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>631</v>
+        <v>824</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2255</v>
+        <v>2063</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1565</v>
+        <v>1526</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>252</v>
+        <v>507</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>260</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>602</v>
+        <v>629</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2282</v>
+        <v>2257</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1576</v>
+        <v>1565</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>469</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>770</v>
+        <v>605</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2113</v>
+        <v>2279</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1118</v>
+        <v>1043</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1500</v>
+        <v>1576</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>249</v>
+        <v>134</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>204</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>751</v>
+        <v>769</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2130</v>
+        <v>2114</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2146</v>
+        <v>2130</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1466</v>
+        <v>1500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>547</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +98,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -523,561 +526,585 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>672</v>
+        <v>873</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2349</v>
+        <v>2148</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>839</v>
+        <v>863</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1801</v>
+        <v>1777</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>200</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>612</v>
+        <v>666</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2408</v>
+        <v>2354</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1818</v>
+        <v>1801</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>698</v>
+        <v>329</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>147</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>409</v>
+        <v>606</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2605</v>
+        <v>2408</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>755</v>
+        <v>822</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1884</v>
+        <v>1817</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>385</v>
+        <v>687</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>254</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>322</v>
+        <v>405</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2683</v>
+        <v>2601</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1915</v>
+        <v>1884</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>97</v>
+        <v>380</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1144</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>418</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>2475</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>834</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1804</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>490</v>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>479</v>
+        <v>420</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2413</v>
+        <v>2472</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>874</v>
+        <v>833</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1764</v>
+        <v>1805</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1053</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>769</v>
+        <v>479</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2122</v>
+        <v>2412</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1003</v>
+        <v>874</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1633</v>
+        <v>1764</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>570</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1002</v>
+        <v>770</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1889</v>
+        <v>2121</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1086</v>
+        <v>1004</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1550</v>
+        <v>1632</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>303</v>
+        <v>125</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>142</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>867</v>
+        <v>999</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2024</v>
+        <v>1892</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1569</v>
+        <v>1550</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>153</v>
+        <v>301</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>430</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>982</v>
+        <v>868</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1909</v>
+        <v>2023</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1552</v>
+        <v>1569</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>345</v>
+        <v>156</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>108</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>853</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1053</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1580</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>287</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>176</v>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>718</v>
+        <v>849</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2173</v>
+        <v>2042</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1029</v>
+        <v>1053</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1604</v>
+        <v>1580</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>640</v>
+        <v>719</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2250</v>
+        <v>2172</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1013</v>
+        <v>1028</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1616</v>
+        <v>1605</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>154</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>543</v>
+        <v>639</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2346</v>
+        <v>2250</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1633</v>
+        <v>1616</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>90</v>
+        <v>293</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>999</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>874</v>
+        <v>541</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2015</v>
+        <v>2348</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1084</v>
+        <v>994</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1541</v>
+        <v>1633</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>259</v>
+        <v>93</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>152</v>
+        <v>997</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>824</v>
+        <v>878</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2063</v>
+        <v>2011</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1099</v>
+        <v>1085</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1526</v>
+        <v>1540</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>507</v>
+        <v>246</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>106</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>629</v>
+        <v>821</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2257</v>
+        <v>2066</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1565</v>
+        <v>1526</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>266</v>
+        <v>521</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>245</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2279</v>
+        <v>2255</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1576</v>
+        <v>1564</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>476</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>769</v>
+        <v>605</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2114</v>
+        <v>2279</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1118</v>
+        <v>1043</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1500</v>
+        <v>1576</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>212</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>751</v>
+        <v>771</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2130</v>
+        <v>2112</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,9 +98,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -526,585 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>873</v>
+        <v>729</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2148</v>
+        <v>2292</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>863</v>
+        <v>790</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1777</v>
+        <v>1851</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>402</v>
+        <v>170</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>154</v>
+        <v>812</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>666</v>
+        <v>864</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2354</v>
+        <v>2156</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>839</v>
+        <v>863</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1801</v>
+        <v>1777</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>329</v>
+        <v>400</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>198</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>606</v>
+        <v>657</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2408</v>
+        <v>2357</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1817</v>
+        <v>1800</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>687</v>
+        <v>317</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>405</v>
+        <v>602</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2601</v>
+        <v>2404</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>755</v>
+        <v>822</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1884</v>
+        <v>1817</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>380</v>
+        <v>682</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>277</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2522</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>756</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1883</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>394</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>247</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>420</v>
+        <v>293</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2472</v>
+        <v>2599</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>833</v>
+        <v>723</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1805</v>
+        <v>1915</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>498</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2412</v>
+        <v>2472</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>874</v>
+        <v>834</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1764</v>
+        <v>1804</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1042</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>770</v>
+        <v>489</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2121</v>
+        <v>2402</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1004</v>
+        <v>876</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1632</v>
+        <v>1762</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>570</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>999</v>
+        <v>765</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1892</v>
+        <v>2126</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1086</v>
+        <v>1004</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1550</v>
+        <v>1632</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>301</v>
+        <v>128</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>143</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>868</v>
+        <v>996</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2023</v>
+        <v>1895</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1067</v>
+        <v>1085</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1569</v>
+        <v>1551</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>156</v>
+        <v>301</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>425</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1570</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>849</v>
+        <v>978</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2042</v>
+        <v>1913</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1580</v>
+        <v>1550</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>264</v>
+        <v>342</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>177</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>719</v>
+        <v>845</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2172</v>
+        <v>2046</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1028</v>
+        <v>1052</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1605</v>
+        <v>1581</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>639</v>
+        <v>720</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2250</v>
+        <v>2170</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1013</v>
+        <v>1028</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1616</v>
+        <v>1605</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>541</v>
+        <v>635</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2348</v>
+        <v>2254</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1633</v>
+        <v>1616</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>93</v>
+        <v>297</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>997</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>878</v>
+        <v>548</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2011</v>
+        <v>2341</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1085</v>
+        <v>994</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1540</v>
+        <v>1633</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>156</v>
+        <v>996</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>821</v>
+        <v>873</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2066</v>
+        <v>2016</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1099</v>
+        <v>1086</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1526</v>
+        <v>1539</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>521</v>
+        <v>260</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>91</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>631</v>
+        <v>823</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2255</v>
+        <v>2064</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1058</v>
+        <v>1099</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1564</v>
+        <v>1526</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>258</v>
+        <v>515</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>253</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2279</v>
+        <v>2257</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1576</v>
+        <v>1564</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>484</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>771</v>
+        <v>607</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2112</v>
+        <v>2277</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1117</v>
+        <v>1043</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1501</v>
+        <v>1576</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>200</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
